--- a/public/templates/modele-import-agents.xlsx
+++ b/public/templates/modele-import-agents.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Agents" sheetId="1" r:id="rId1"/>
+    <sheet name="Consignes" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,115 +398,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I3"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" xml:space="preserve">
+    <row r="1">
       <c r="A1" t="str">
+        <v>Matricule</v>
+      </c>
+      <c r="B1" t="str">
         <v>Nom</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Prénom</v>
       </c>
-      <c r="C1" t="str" xml:space="preserve">
-        <v xml:space="preserve">Matricule(collaborateurs)
-Téléphone(client externe)</v>
-      </c>
       <c r="D1" t="str">
+        <v>Sexe</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Nationalité</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Emploi</v>
+      </c>
+      <c r="G1" t="str">
         <v>Service</v>
       </c>
-      <c r="E1" t="str" xml:space="preserve">
-        <v xml:space="preserve">Département
-(Dsm/Manut/Entrepot)</v>
-      </c>
-      <c r="F1" t="str" xml:space="preserve">
-        <v xml:space="preserve">Statut
-[Agent ou Manager]</v>
-      </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>Département</v>
+      </c>
+      <c r="I1" t="str">
         <v>Direction</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>MAT-001</v>
+      </c>
+      <c r="B2" t="str">
         <v>KONE</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>Moussa</v>
       </c>
-      <c r="C2" t="str">
-        <v>MAT-001</v>
-      </c>
       <c r="D2" t="str">
-        <v>Logistique</v>
+        <v>M</v>
       </c>
       <c r="E2" t="str">
-        <v>Dsm</v>
+        <v>Ivoirienne</v>
       </c>
       <c r="F2" t="str">
-        <v>Agent</v>
+        <v>Agent de transit</v>
       </c>
       <c r="G2" t="str">
+        <v>Transit</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Opérations maritimes</v>
+      </c>
+      <c r="I2" t="str">
         <v>DSM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>MAT-002</v>
+      </c>
+      <c r="B3" t="str">
         <v>DIALLO</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>Aminata</v>
       </c>
-      <c r="C3" t="str">
-        <v>MAT-002</v>
-      </c>
       <c r="D3" t="str">
-        <v>Comptabilité</v>
+        <v>F</v>
       </c>
       <c r="E3" t="str">
-        <v>Manut</v>
+        <v>Ivoirienne</v>
       </c>
       <c r="F3" t="str">
-        <v>Manager</v>
+        <v>Comptable</v>
       </c>
       <c r="G3" t="str">
+        <v>Facturation</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Finance &amp; Clients</v>
+      </c>
+      <c r="I3" t="str">
         <v>DSM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <cols>
+    <col min="1" max="1" width="110.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Consignes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Une ligne par agent. Le matricule identifie l’agent : s’il existe déjà, sa fiche est mise à jour, sinon il est créé.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sexe : M ou F.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SOCIÉTÉ CLIENTE</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Contact</v>
-      </c>
-      <c r="C4" t="str">
-        <v>0707070707</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>Client</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>Une cellule vide ne modifie pas la valeur déjà enregistrée.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Le rôle (agent / manager) n’est pas modifié par ce fichier : il se gère dans la fiche de l’agent.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Les agents absents du fichier ne sont ni modifiés ni supprimés.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
 </file>